--- a/artfynd/A 44309-2025 artfynd.xlsx
+++ b/artfynd/A 44309-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2124,10 +2124,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>61381315</v>
+        <v>54548215</v>
       </c>
       <c r="B14" t="n">
-        <v>103813</v>
+        <v>95511</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2136,25 +2136,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>221944</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636695.1523861155</v>
+        <v>636485.9746798918</v>
       </c>
       <c r="R14" t="n">
-        <v>6556256.244530094</v>
+        <v>6556262.12119995</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ca 70-årig ask med delvis torra grenar.</t>
+          <t>På litet block.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2244,7 +2244,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>61381618</v>
+        <v>61381315</v>
       </c>
       <c r="B15" t="n">
         <v>103813</v>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636481.920650503</v>
+        <v>636695.1523861155</v>
       </c>
       <c r="R15" t="n">
-        <v>6556346.749863084</v>
+        <v>6556256.244530094</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka friska askar och almar ca 60-70 år gamla.</t>
+          <t>Ca 70-årig ask med delvis torra grenar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,10 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>61381435</v>
+        <v>61381618</v>
       </c>
       <c r="B16" t="n">
-        <v>93148</v>
+        <v>103813</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2376,25 +2376,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1079</v>
+        <v>220785</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636599.7792942427</v>
+        <v>636481.920650503</v>
       </c>
       <c r="R16" t="n">
-        <v>6556246.152611361</v>
+        <v>6556346.749863084</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Nytt fynd på västra sidan av stammen på äldre lönn, från marken och upp till ca 1m över marken. Brösthöjdsdiameter 25cm.</t>
+          <t>Enstaka friska askar och almar ca 60-70 år gamla.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2484,7 +2484,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>61379079</v>
+        <v>61381435</v>
       </c>
       <c r="B17" t="n">
         <v>93148</v>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636712.8150185787</v>
+        <v>636599.7792942427</v>
       </c>
       <c r="R17" t="n">
-        <v>6556179.807821023</v>
+        <v>6556246.152611361</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Samma fynd som 2015. Vid roten av gammal lönn ca 2x3dm och ca 1x5dm ca 2m över marken på norra sidan av trädet. Även lunglav på samma träd.</t>
+          <t>Nytt fynd på västra sidan av stammen på äldre lönn, från marken och upp till ca 1m över marken. Brösthöjdsdiameter 25cm.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2604,10 +2604,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>61381720</v>
+        <v>61379079</v>
       </c>
       <c r="B18" t="n">
-        <v>88270</v>
+        <v>93148</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2616,48 +2616,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>655</v>
+        <v>1079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636481.8973634914</v>
+        <v>636712.8150185787</v>
       </c>
       <c r="R18" t="n">
-        <v>6556217.789733715</v>
+        <v>6556179.807821023</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2704,7 +2697,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På grov ek ca 6-7m över marken. Eken står nära bergbrant och har håligheter med mulm och grov skorpbark.</t>
+          <t>Samma fynd som 2015. Vid roten av gammal lönn ca 2x3dm och ca 1x5dm ca 2m över marken på norra sidan av trädet. Även lunglav på samma träd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2713,7 +2706,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2732,10 +2724,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>61381322</v>
+        <v>61381720</v>
       </c>
       <c r="B19" t="n">
-        <v>103813</v>
+        <v>88270</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2744,41 +2736,48 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220785</v>
+        <v>655</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Schaeff.) With., nom sanct.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636662.070112007</v>
+        <v>636481.8973634914</v>
       </c>
       <c r="R19" t="n">
-        <v>6556260.198370786</v>
+        <v>6556217.789733715</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2825,7 +2824,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Frisk ask ca 70 år gammal.</t>
+          <t>På grov ek ca 6-7m över marken. Eken står nära bergbrant och har håligheter med mulm och grov skorpbark.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2834,6 +2833,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>61381465</v>
+        <v>61381322</v>
       </c>
       <c r="B20" t="n">
-        <v>93148</v>
+        <v>103813</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2864,25 +2864,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1079</v>
+        <v>220785</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636590.801830634</v>
+        <v>636662.070112007</v>
       </c>
       <c r="R20" t="n">
-        <v>6556238.124669672</v>
+        <v>6556260.198370786</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Nytt fynd på östra sidan av äldre lönn. Ca 15x20cm, 1m över marken. Brösthöjdsdiameter 30cm.</t>
+          <t>Frisk ask ca 70 år gammal.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2972,10 +2972,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>61378955</v>
+        <v>61381465</v>
       </c>
       <c r="B21" t="n">
-        <v>73698</v>
+        <v>93148</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2984,40 +2984,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>1079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636705.0304978063</v>
+        <v>636590.801830634</v>
       </c>
       <c r="R21" t="n">
-        <v>6556195.970665244</v>
+        <v>6556238.124669672</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3064,7 +3065,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal ek.</t>
+          <t>Nytt fynd på östra sidan av äldre lönn. Ca 15x20cm, 1m över marken. Brösthöjdsdiameter 30cm.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3091,10 +3092,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>61381579</v>
+        <v>61378955</v>
       </c>
       <c r="B22" t="n">
-        <v>103346</v>
+        <v>73698</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3103,41 +3104,40 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221423</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636474.8159383975</v>
+        <v>636705.0304978063</v>
       </c>
       <c r="R22" t="n">
-        <v>6556343.927077802</v>
+        <v>6556195.970665244</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3180,6 +3180,11 @@
       <c r="AB22" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal ek.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3206,10 +3211,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>61381657</v>
+        <v>61381579</v>
       </c>
       <c r="B23" t="n">
-        <v>94121</v>
+        <v>103346</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3218,25 +3223,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>221423</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3249,10 +3254,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636477.1981740498</v>
+        <v>636474.8159383975</v>
       </c>
       <c r="R23" t="n">
-        <v>6556234.063059719</v>
+        <v>6556343.927077802</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3295,11 +3300,6 @@
       <c r="AB23" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gammal rötskadad granlåga.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3326,10 +3326,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>61378960</v>
+        <v>61381657</v>
       </c>
       <c r="B24" t="n">
-        <v>98520</v>
+        <v>94121</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3338,25 +3338,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636705.0304978063</v>
+        <v>636477.1981740498</v>
       </c>
       <c r="R24" t="n">
-        <v>6556195.970665244</v>
+        <v>6556234.063059719</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Allmänt förekommande.</t>
+          <t>På gammal rötskadad granlåga.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3446,10 +3446,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>61381723</v>
+        <v>61378960</v>
       </c>
       <c r="B25" t="n">
-        <v>89350</v>
+        <v>98520</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3458,40 +3458,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5445</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636501.121715354</v>
+        <v>636705.0304978063</v>
       </c>
       <c r="R25" t="n">
-        <v>6556299.141143036</v>
+        <v>6556195.970665244</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3538,7 +3539,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På nedfallen ekgren och troligen högt upp i trädkronan på gammal ek.</t>
+          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3547,7 +3548,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3566,10 +3566,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>61381396</v>
+        <v>61381723</v>
       </c>
       <c r="B26" t="n">
-        <v>93148</v>
+        <v>89350</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3578,41 +3578,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1079</v>
+        <v>5445</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636595.8689769331</v>
+        <v>636501.121715354</v>
       </c>
       <c r="R26" t="n">
-        <v>6556254.747131445</v>
+        <v>6556299.141143036</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3659,7 +3658,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Nytt fynd vid basen av död ask mellan två block, 25cm i brösthöjdsdiameter.</t>
+          <t>På nedfallen ekgren och troligen högt upp i trädkronan på gammal ek.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3668,6 +3667,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>61378962</v>
+        <v>61381396</v>
       </c>
       <c r="B27" t="n">
-        <v>99398</v>
+        <v>93148</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3698,25 +3698,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>1079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636710.9054743795</v>
+        <v>636595.8689769331</v>
       </c>
       <c r="R27" t="n">
-        <v>6556190.015415868</v>
+        <v>6556254.747131445</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Spridda fynd i området.</t>
+          <t>Nytt fynd vid basen av död ask mellan två block, 25cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3806,10 +3806,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>61381611</v>
+        <v>61378962</v>
       </c>
       <c r="B28" t="n">
-        <v>100515</v>
+        <v>99398</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3818,25 +3818,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223246</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636481.920650503</v>
+        <v>636710.9054743795</v>
       </c>
       <c r="R28" t="n">
-        <v>6556346.749863084</v>
+        <v>6556190.015415868</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Enstaka friska almar och askar ca 60-70 år gamla.</t>
+          <t>Spridda fynd i området.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3926,10 +3926,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>61381592</v>
+        <v>61381611</v>
       </c>
       <c r="B29" t="n">
-        <v>99398</v>
+        <v>100515</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3938,25 +3938,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221235</v>
+        <v>223246</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636474.8159383975</v>
+        <v>636481.920650503</v>
       </c>
       <c r="R29" t="n">
-        <v>6556343.927077802</v>
+        <v>6556346.749863084</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Spridda fynd på delvis kalkhaltig mark.</t>
+          <t>Enstaka friska almar och askar ca 60-70 år gamla.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4046,10 +4046,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>61381309</v>
+        <v>61381592</v>
       </c>
       <c r="B30" t="n">
-        <v>89692</v>
+        <v>99398</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4058,40 +4058,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>721</v>
+        <v>221235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Grifola frondosa</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Gray</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636733.9810658585</v>
+        <v>636474.8159383975</v>
       </c>
       <c r="R30" t="n">
-        <v>6556249.927765722</v>
+        <v>6556343.927077802</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4138,7 +4139,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ca 2x2dm vid roten på gammal ek.</t>
+          <t>Spridda fynd på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4147,7 +4148,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4166,10 +4166,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>61379080</v>
+        <v>61381309</v>
       </c>
       <c r="B31" t="n">
-        <v>78569</v>
+        <v>89692</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4182,21 +4182,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>721</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Grifola frondosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Gray</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636712.8150185787</v>
+        <v>636733.9810658585</v>
       </c>
       <c r="R31" t="n">
-        <v>6556179.807821023</v>
+        <v>6556249.927765722</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal lönn.</t>
+          <t>Ca 2x2dm vid roten på gammal ek.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4267,6 +4267,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4285,10 +4286,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>61381728</v>
+        <v>61379080</v>
       </c>
       <c r="B32" t="n">
-        <v>103346</v>
+        <v>78569</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4297,41 +4298,40 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221423</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636606.0576544527</v>
+        <v>636712.8150185787</v>
       </c>
       <c r="R32" t="n">
-        <v>6556200.135970805</v>
+        <v>6556179.807821023</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4378,7 +4378,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Enstaka fyndplatser på kalkhaltig mark.</t>
+          <t>På gammal lönn.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4405,10 +4405,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>73738381</v>
+        <v>61381728</v>
       </c>
       <c r="B33" t="n">
-        <v>73686</v>
+        <v>103346</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4417,43 +4417,44 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>308</v>
+        <v>221423</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>NV Yngsviken, Sjundaskogen, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636495.0078162361</v>
+        <v>636606.0576544527</v>
       </c>
       <c r="R33" t="n">
-        <v>6556282.995396274</v>
+        <v>6556200.135970805</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4477,7 +4478,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2018-10-20</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4487,7 +4488,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2018-10-20</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4495,32 +4496,36 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Enstaka fyndplatser på kalkhaltig mark.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>73738383</v>
+        <v>73738381</v>
       </c>
       <c r="B34" t="n">
         <v>73686</v>
@@ -4562,10 +4567,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636503.9665517998</v>
+        <v>636495.0078162361</v>
       </c>
       <c r="R34" t="n">
-        <v>6556277.150226528</v>
+        <v>6556282.995396274</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4635,10 +4640,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>73738385</v>
+        <v>73738383</v>
       </c>
       <c r="B35" t="n">
-        <v>88270</v>
+        <v>73686</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4651,21 +4656,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>655</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4750,10 +4755,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>73746190</v>
+        <v>73738385</v>
       </c>
       <c r="B36" t="n">
-        <v>103346</v>
+        <v>88270</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4762,42 +4767,40 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221423</v>
+        <v>655</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>NV Yngsviken, Sjundaskogen, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636513.880450511</v>
+        <v>636503.9665517998</v>
       </c>
       <c r="R36" t="n">
-        <v>6556287.780260329</v>
+        <v>6556277.150226528</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4824,7 +4827,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4834,7 +4837,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -4860,17 +4863,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>73746167</v>
+        <v>73746190</v>
       </c>
       <c r="B37" t="n">
-        <v>73507</v>
+        <v>103346</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4883,36 +4886,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6428</v>
+        <v>221423</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636596.7869340511</v>
+        <v>636513.880450511</v>
       </c>
       <c r="R37" t="n">
-        <v>6556257.862686821</v>
+        <v>6556287.780260329</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4982,10 +4987,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>73746181</v>
+        <v>73746167</v>
       </c>
       <c r="B38" t="n">
-        <v>93148</v>
+        <v>73507</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4994,41 +4999,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1079</v>
+        <v>6428</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636609.784727848</v>
+        <v>636596.7869340511</v>
       </c>
       <c r="R38" t="n">
-        <v>6556239.831263402</v>
+        <v>6556257.862686821</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5098,10 +5102,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>73746191</v>
+        <v>73746181</v>
       </c>
       <c r="B39" t="n">
-        <v>98520</v>
+        <v>93148</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5110,42 +5114,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>1079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>636513.880450511</v>
+        <v>636609.784727848</v>
       </c>
       <c r="R39" t="n">
-        <v>6556287.780260329</v>
+        <v>6556239.831263402</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5215,7 +5218,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>73746035</v>
+        <v>73746191</v>
       </c>
       <c r="B40" t="n">
         <v>98520</v>
@@ -5259,10 +5262,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>636516.7799732704</v>
+        <v>636513.880450511</v>
       </c>
       <c r="R40" t="n">
-        <v>6556249.863879045</v>
+        <v>6556287.780260329</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5332,10 +5335,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>73746192</v>
+        <v>73746035</v>
       </c>
       <c r="B41" t="n">
-        <v>99398</v>
+        <v>98520</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5348,21 +5351,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5376,10 +5379,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>636513.880450511</v>
+        <v>636516.7799732704</v>
       </c>
       <c r="R41" t="n">
-        <v>6556287.780260329</v>
+        <v>6556249.863879045</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5449,10 +5452,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>73746032</v>
+        <v>73746192</v>
       </c>
       <c r="B42" t="n">
-        <v>78603</v>
+        <v>99398</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5465,36 +5468,38 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>221235</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636516.7799732704</v>
+        <v>636513.880450511</v>
       </c>
       <c r="R42" t="n">
-        <v>6556249.863879045</v>
+        <v>6556287.780260329</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5564,10 +5569,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>73746059</v>
+        <v>73746032</v>
       </c>
       <c r="B43" t="n">
-        <v>98520</v>
+        <v>78603</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5580,38 +5585,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636713.0170853264</v>
+        <v>636516.7799732704</v>
       </c>
       <c r="R43" t="n">
-        <v>6556174.163268562</v>
+        <v>6556249.863879045</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5681,10 +5684,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>73746176</v>
+        <v>73746059</v>
       </c>
       <c r="B44" t="n">
-        <v>93148</v>
+        <v>98520</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5693,41 +5696,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1079</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>V yngsviken, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>636599.0633518201</v>
+        <v>636713.0170853264</v>
       </c>
       <c r="R44" t="n">
-        <v>6556251.778668512</v>
+        <v>6556174.163268562</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5797,7 +5801,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>73746160</v>
+        <v>73746176</v>
       </c>
       <c r="B45" t="n">
         <v>93148</v>
@@ -5836,14 +5840,14 @@
       <c r="L45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>V yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>636596.7869340511</v>
+        <v>636599.0633518201</v>
       </c>
       <c r="R45" t="n">
-        <v>6556257.862686821</v>
+        <v>6556251.778668512</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5913,10 +5917,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>73746028</v>
+        <v>73746160</v>
       </c>
       <c r="B46" t="n">
-        <v>78569</v>
+        <v>93148</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5925,40 +5929,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>1079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>636516.7799732704</v>
+        <v>636596.7869340511</v>
       </c>
       <c r="R46" t="n">
-        <v>6556249.863879045</v>
+        <v>6556257.862686821</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6028,10 +6033,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>73746170</v>
+        <v>73746028</v>
       </c>
       <c r="B47" t="n">
-        <v>99398</v>
+        <v>78569</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6040,42 +6045,40 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>636596.7869340511</v>
+        <v>636516.7799732704</v>
       </c>
       <c r="R47" t="n">
-        <v>6556257.862686821</v>
+        <v>6556249.863879045</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6145,7 +6148,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>73746056</v>
+        <v>73746170</v>
       </c>
       <c r="B48" t="n">
         <v>99398</v>
@@ -6189,10 +6192,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>636713.0170853264</v>
+        <v>636596.7869340511</v>
       </c>
       <c r="R48" t="n">
-        <v>6556174.163268562</v>
+        <v>6556257.862686821</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6262,7 +6265,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>73746042</v>
+        <v>73746056</v>
       </c>
       <c r="B49" t="n">
         <v>99398</v>
@@ -6306,10 +6309,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>636516.7799732704</v>
+        <v>636713.0170853264</v>
       </c>
       <c r="R49" t="n">
-        <v>6556249.863879045</v>
+        <v>6556174.163268562</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6379,10 +6382,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>73746052</v>
+        <v>73746042</v>
       </c>
       <c r="B50" t="n">
-        <v>78569</v>
+        <v>99398</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6391,40 +6394,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>636713.0170853264</v>
+        <v>636516.7799732704</v>
       </c>
       <c r="R50" t="n">
-        <v>6556174.163268562</v>
+        <v>6556249.863879045</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6494,10 +6499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>73746055</v>
+        <v>73746052</v>
       </c>
       <c r="B51" t="n">
-        <v>93148</v>
+        <v>78569</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6506,31 +6511,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
@@ -6610,10 +6614,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>73746038</v>
+        <v>73746055</v>
       </c>
       <c r="B52" t="n">
-        <v>78602</v>
+        <v>93148</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6622,40 +6626,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>1079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>636516.7799732704</v>
+        <v>636713.0170853264</v>
       </c>
       <c r="R52" t="n">
-        <v>6556249.863879045</v>
+        <v>6556174.163268562</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6725,10 +6730,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>73746183</v>
+        <v>73746038</v>
       </c>
       <c r="B53" t="n">
-        <v>93148</v>
+        <v>78602</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6737,41 +6742,40 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1079</v>
+        <v>6463</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>636585.9733916385</v>
+        <v>636516.7799732704</v>
       </c>
       <c r="R53" t="n">
-        <v>6556229.217546627</v>
+        <v>6556249.863879045</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6841,10 +6845,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>73746040</v>
+        <v>73746183</v>
       </c>
       <c r="B54" t="n">
-        <v>78458</v>
+        <v>93148</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6853,40 +6857,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6457</v>
+        <v>1079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>636516.7799732704</v>
+        <v>636585.9733916385</v>
       </c>
       <c r="R54" t="n">
-        <v>6556249.863879045</v>
+        <v>6556229.217546627</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6953,6 +6958,121 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>73746040</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78458</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>636516.7799732704</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6556249.863879045</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44309-2025 artfynd.xlsx
+++ b/artfynd/A 44309-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54527561</v>
+        <v>61381657</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,36 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636707.9500379404</v>
+        <v>636477</v>
       </c>
       <c r="R2" t="n">
-        <v>6556171.926682174</v>
+        <v>6556234</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -747,27 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre lönn</t>
+          <t>På gammal rötskadad granlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,37 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54527447</v>
+        <v>73746220</v>
       </c>
       <c r="B3" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>93</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ekpricklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Inoderma byssaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Weigel) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,17 +813,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636695.2270598781</v>
+        <v>636482</v>
       </c>
       <c r="R3" t="n">
-        <v>6556182.261026392</v>
+        <v>6556212</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,27 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammal ek., nyligen frihuggen.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,33 +861,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54527514</v>
+        <v>73738380</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,21 +891,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,17 +913,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>NV Yngsviken, Sjundaskogen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636695.8513155582</v>
+        <v>636447</v>
       </c>
       <c r="R4" t="n">
-        <v>6556179.200582761</v>
+        <v>6556318</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,27 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På samma lönn som aspfjädermossan.</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,82 +961,69 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54527501</v>
+        <v>73738381</v>
       </c>
       <c r="B5" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1079</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>NV Yngsviken, Sjundaskogen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636695.8513155582</v>
+        <v>636495</v>
       </c>
       <c r="R5" t="n">
-        <v>6556179.200582761</v>
+        <v>6556283</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,27 +1047,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 5 dm2 vid basen av äldre lönn och ca 4 dm2 2m över marken, norra sidan. Strax norr om bilväg. Lönnen och en stor del av ädellövträden nyligen frihuggna. Möjligen mer mossa högre upp på lönnen.</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,33 +1061,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54548306</v>
+        <v>73738383</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,17 +1113,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>NV Yngsviken, Sjundaskogen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636517.0738926937</v>
+        <v>636504</v>
       </c>
       <c r="R6" t="n">
-        <v>6556256.039822619</v>
+        <v>6556277</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,27 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På klen lönn med även luddlav.</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,55 +1161,51 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54548293</v>
+        <v>73746197</v>
       </c>
       <c r="B7" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Parknål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca hispidula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,17 +1213,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636517.0738926937</v>
+        <v>636440</v>
       </c>
       <c r="R7" t="n">
-        <v>6556256.039822619</v>
+        <v>6556324</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,27 +1247,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På klen lönn med även lunglav.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,71 +1261,66 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>54548147</v>
+        <v>54548193</v>
       </c>
       <c r="B8" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83304</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636476.9087312364</v>
+        <v>636448</v>
       </c>
       <c r="R8" t="n">
-        <v>6556342.97432366</v>
+        <v>6556321</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,24 +1350,14 @@
           <t>2015-07-22</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2015-07-22</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka levande yngre ask som nyligen frihuggits från konkurrerande barrträd.</t>
+          <t>Gammal ek.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,53 +1384,55 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>54548048</v>
+        <v>61381720</v>
       </c>
       <c r="B9" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>655</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Schaeff.) With., nom sanct.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636650.9632729907</v>
+        <v>636482</v>
       </c>
       <c r="R9" t="n">
-        <v>6556239.763170176</v>
+        <v>6556218</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1591,27 +1459,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Två levande medelålders askar som nyligen frihuggits från konkurrerande barrträd.</t>
+          <t>På grov ek ca 6-7m över marken. Eken står nära bergbrant och har håligheter med mulm och grov skorpbark.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,6 +1478,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1638,56 +1497,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>54548104</v>
+        <v>73738385</v>
       </c>
       <c r="B10" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223246</v>
+        <v>655</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>NV Yngsviken, Sjundaskogen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636495.0459869215</v>
+        <v>636504</v>
       </c>
       <c r="R10" t="n">
-        <v>6556325.126662954</v>
+        <v>6556277</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1711,27 +1564,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>En levande toppbruten alm som nyligen frihuggits från konkurrerande barrträd.</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,33 +1578,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>54548265</v>
+        <v>73746234</v>
       </c>
       <c r="B11" t="n">
-        <v>9259</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,46 +1608,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101254</v>
+        <v>655</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skeppsvarvsfluga</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lymexylon navale</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636494.8585575026</v>
+        <v>636482</v>
       </c>
       <c r="R11" t="n">
-        <v>6556215.170224692</v>
+        <v>6556212</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1837,27 +1664,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gamla kläckhål på gammal grov ek med håligheter och mulm. Nära bergbrant.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,74 +1678,69 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>54548136</v>
+        <v>73738378</v>
       </c>
       <c r="B12" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223246</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>NV Yngsviken, Sjundaskogen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636476.9087312364</v>
+        <v>636447</v>
       </c>
       <c r="R12" t="n">
-        <v>6556342.97432366</v>
+        <v>6556318</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1957,27 +1764,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Enstaka yngra levande frihuggna almar. Inslag av gammal ek enstaka yngre ask och lönn.</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,33 +1778,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>54547951</v>
+        <v>54548230</v>
       </c>
       <c r="B13" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,37 +1808,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636712.8499114477</v>
+        <v>636494</v>
       </c>
       <c r="R13" t="n">
-        <v>6556265.098652583</v>
+        <v>6556204</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2080,24 +1870,14 @@
           <t>2015-07-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2015-07-22</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Källpåverkad strandzon med en liten ringsatt källa.</t>
+          <t>På lodyta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2106,6 +1886,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2124,53 +1905,47 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>54548215</v>
+        <v>61381723</v>
       </c>
       <c r="B14" t="n">
-        <v>95511</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221944</v>
+        <v>5445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636485.9746798918</v>
+        <v>636501</v>
       </c>
       <c r="R14" t="n">
-        <v>6556262.12119995</v>
+        <v>6556299</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2197,27 +1972,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2015-07-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På litet block.</t>
+          <t>På nedfallen ekgren och troligen högt upp i trädkronan på gammal ek.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2226,6 +1991,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2244,56 +2010,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>61381315</v>
+        <v>73738379</v>
       </c>
       <c r="B15" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220785</v>
+        <v>6428</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>NV Yngsviken, Sjundaskogen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636695.1523861155</v>
+        <v>636447</v>
       </c>
       <c r="R15" t="n">
-        <v>6556256.244530094</v>
+        <v>6556318</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2317,27 +2077,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ca 70-årig ask med delvis torra grenar.</t>
+          <t>2018-10-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2346,74 +2091,69 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>61381618</v>
+        <v>73746196</v>
       </c>
       <c r="B16" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>6428</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636481.920650503</v>
+        <v>636440</v>
       </c>
       <c r="R16" t="n">
-        <v>6556346.749863084</v>
+        <v>6556324</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2437,27 +2177,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Enstaka friska askar och almar ca 60-70 år gamla.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2466,74 +2191,69 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>61381435</v>
+        <v>73746214</v>
       </c>
       <c r="B17" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78728</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1079</v>
+        <v>6436</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636599.7792942427</v>
+        <v>636482</v>
       </c>
       <c r="R17" t="n">
-        <v>6556246.152611361</v>
+        <v>6556212</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2557,27 +2277,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Nytt fynd på västra sidan av stammen på äldre lönn, från marken och upp till ca 1m över marken. Brösthöjdsdiameter 25cm.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,74 +2291,69 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>61379079</v>
+        <v>73746237</v>
       </c>
       <c r="B18" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1079</v>
+        <v>6443</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636712.8150185787</v>
+        <v>636482</v>
       </c>
       <c r="R18" t="n">
-        <v>6556179.807821023</v>
+        <v>6556212</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2677,27 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Samma fynd som 2015. Vid roten av gammal lönn ca 2x3dm och ca 1x5dm ca 2m över marken på norra sidan av trädet. Även lunglav på samma träd.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2706,81 +2391,69 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>61381720</v>
+        <v>73746040</v>
       </c>
       <c r="B19" t="n">
-        <v>88270</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>655</v>
+        <v>6457</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636481.8973634914</v>
+        <v>636517</v>
       </c>
       <c r="R19" t="n">
-        <v>6556217.789733715</v>
+        <v>6556250</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2804,27 +2477,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På grov ek ca 6-7m över marken. Eken står nära bergbrant och har håligheter med mulm och grov skorpbark.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2840,65 +2498,59 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>61381322</v>
+        <v>54548306</v>
       </c>
       <c r="B20" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220785</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636662.070112007</v>
+        <v>636517</v>
       </c>
       <c r="R20" t="n">
-        <v>6556260.198370786</v>
+        <v>6556256</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2925,27 +2577,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Frisk ask ca 70 år gammal.</t>
+          <t>På klen lönn med även luddlav.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2972,56 +2614,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>61381465</v>
+        <v>73746028</v>
       </c>
       <c r="B21" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636590.801830634</v>
+        <v>636517</v>
       </c>
       <c r="R21" t="n">
-        <v>6556238.124669672</v>
+        <v>6556250</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3045,27 +2681,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Nytt fynd på östra sidan av äldre lönn. Ca 15x20cm, 1m över marken. Brösthöjdsdiameter 30cm.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3074,55 +2695,51 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>61378955</v>
+        <v>73746038</v>
       </c>
       <c r="B22" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3130,17 +2747,17 @@
       <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636705.0304978063</v>
+        <v>636517</v>
       </c>
       <c r="R22" t="n">
-        <v>6556195.970665244</v>
+        <v>6556250</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3164,27 +2781,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gammal ek.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3193,33 +2795,29 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>61381579</v>
+        <v>54548293</v>
       </c>
       <c r="B23" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,37 +2825,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221423</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636474.8159383975</v>
+        <v>636517</v>
       </c>
       <c r="R23" t="n">
-        <v>6556343.927077802</v>
+        <v>6556256</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3284,22 +2881,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På klen lönn med även lunglav.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3326,56 +2918,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>61381657</v>
+        <v>73746032</v>
       </c>
       <c r="B24" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636477.1981740498</v>
+        <v>636517</v>
       </c>
       <c r="R24" t="n">
-        <v>6556234.063059719</v>
+        <v>6556250</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3399,27 +2985,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gammal rötskadad granlåga.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3428,71 +2999,73 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>61378960</v>
+        <v>54548265</v>
       </c>
       <c r="B25" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9363</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>101254</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skeppsvarvsfluga</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lymexylon navale</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636705.0304978063</v>
+        <v>636495</v>
       </c>
       <c r="R25" t="n">
-        <v>6556195.970665244</v>
+        <v>6556215</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3519,27 +3092,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Allmänt förekommande.</t>
+          <t>Gamla kläckhål på gammal grov ek med håligheter och mulm. Nära bergbrant.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3566,52 +3129,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>61381723</v>
+        <v>54548147</v>
       </c>
       <c r="B26" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5445</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636501.121715354</v>
+        <v>636477</v>
       </c>
       <c r="R26" t="n">
-        <v>6556299.141143036</v>
+        <v>6556343</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3638,27 +3197,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På nedfallen ekgren och troligen högt upp i trädkronan på gammal ek.</t>
+          <t>Enstaka levande yngre ask som nyligen frihuggits från konkurrerande barrträd.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3667,7 +3216,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3686,37 +3234,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>61381396</v>
+        <v>61381618</v>
       </c>
       <c r="B27" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1079</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3729,10 +3272,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636595.8689769331</v>
+        <v>636482</v>
       </c>
       <c r="R27" t="n">
-        <v>6556254.747131445</v>
+        <v>6556347</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3762,24 +3305,14 @@
           <t>2016-09-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2016-09-09</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Nytt fynd vid basen av död ask mellan två block, 25cm i brösthöjdsdiameter.</t>
+          <t>Enstaka friska askar och almar ca 60-70 år gamla.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3806,19 +3339,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>61378962</v>
+        <v>61381592</v>
       </c>
       <c r="B28" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3849,10 +3377,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636710.9054743795</v>
+        <v>636475</v>
       </c>
       <c r="R28" t="n">
-        <v>6556190.015415868</v>
+        <v>6556344</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3882,24 +3410,14 @@
           <t>2016-09-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2016-09-09</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Spridda fynd i området.</t>
+          <t>Spridda fynd på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3926,56 +3444,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>61381611</v>
+        <v>73746042</v>
       </c>
       <c r="B29" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>223246</v>
+        <v>221235</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636481.920650503</v>
+        <v>636517</v>
       </c>
       <c r="R29" t="n">
-        <v>6556346.749863084</v>
+        <v>6556250</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3999,27 +3513,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Enstaka friska almar och askar ca 60-70 år gamla.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4028,37 +3527,33 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>61381592</v>
+        <v>73746192</v>
       </c>
       <c r="B30" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4083,19 +3578,20 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636474.8159383975</v>
+        <v>636514</v>
       </c>
       <c r="R30" t="n">
-        <v>6556343.927077802</v>
+        <v>6556288</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4119,27 +3615,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Spridda fynd på delvis kalkhaltig mark.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4148,70 +3629,67 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>61381309</v>
+        <v>54548179</v>
       </c>
       <c r="B31" t="n">
-        <v>89692</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>721</v>
+        <v>221423</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallticka</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Grifola frondosa</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Gray</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636733.9810658585</v>
+        <v>636473</v>
       </c>
       <c r="R31" t="n">
-        <v>6556249.927765722</v>
+        <v>6556350</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4238,27 +3716,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ca 2x2dm vid roten på gammal ek.</t>
+          <t>Ett ganska stort bestånd av myskmadra i svag sluttning mot berg. Naturvårdande skötsel har nyligen gjorts i form av frihuggning av ädla lövträd från konkurrerande barrträd.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4267,7 +3735,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4286,52 +3753,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>61379080</v>
+        <v>61381579</v>
       </c>
       <c r="B32" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>221423</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636712.8150185787</v>
+        <v>636475</v>
       </c>
       <c r="R32" t="n">
-        <v>6556179.807821023</v>
+        <v>6556344</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4361,24 +3824,9 @@
           <t>2016-09-09</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gammal lönn.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4405,15 +3853,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>61381728</v>
+        <v>73746190</v>
       </c>
       <c r="B33" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4442,19 +3885,20 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sarvsjön, NO om, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636606.0576544527</v>
+        <v>636514</v>
       </c>
       <c r="R33" t="n">
-        <v>6556200.135970805</v>
+        <v>6556288</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4478,27 +3922,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2016-09-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Enstaka fyndplatser på kalkhaltig mark.</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4507,73 +3936,66 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>73738381</v>
+        <v>54548215</v>
       </c>
       <c r="B34" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>221944</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>NV Yngsviken, Sjundaskogen, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636495.0078162361</v>
+        <v>636486</v>
       </c>
       <c r="R34" t="n">
-        <v>6556282.995396274</v>
+        <v>6556262</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4597,22 +4019,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2018-10-20</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2018-10-20</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På litet block.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4621,71 +4038,67 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>73738383</v>
+        <v>73746035</v>
       </c>
       <c r="B35" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>NV Yngsviken, Sjundaskogen, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>636503.9665517998</v>
+        <v>636517</v>
       </c>
       <c r="R35" t="n">
-        <v>6556277.150226528</v>
+        <v>6556250</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4712,22 +4125,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2018-10-20</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2018-10-20</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4748,59 +4151,56 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>73738385</v>
+        <v>73746191</v>
       </c>
       <c r="B36" t="n">
-        <v>88270</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>655</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>NV Yngsviken, Sjundaskogen, Srm</t>
+          <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636503.9665517998</v>
+        <v>636514</v>
       </c>
       <c r="R36" t="n">
-        <v>6556277.150226528</v>
+        <v>6556288</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4827,22 +4227,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2018-10-20</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2018-10-20</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4863,22 +4253,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>73746190</v>
+        <v>73746245</v>
       </c>
       <c r="B37" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4886,21 +4271,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221423</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4914,10 +4299,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636513.880450511</v>
+        <v>636482</v>
       </c>
       <c r="R37" t="n">
-        <v>6556287.780260329</v>
+        <v>6556212</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4947,19 +4332,9 @@
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4987,55 +4362,51 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>73746167</v>
+        <v>54548104</v>
       </c>
       <c r="B38" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6428</v>
+        <v>223246</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636596.7869340511</v>
+        <v>636495</v>
       </c>
       <c r="R38" t="n">
-        <v>6556257.862686821</v>
+        <v>6556325</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5059,22 +4430,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>En levande toppbruten alm som nyligen frihuggits från konkurrerande barrträd.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5083,56 +4449,50 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>73746181</v>
+        <v>54548136</v>
       </c>
       <c r="B39" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1079</v>
+        <v>223246</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5141,17 +4501,17 @@
       <c r="L39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>636609.784727848</v>
+        <v>636477</v>
       </c>
       <c r="R39" t="n">
-        <v>6556239.831263402</v>
+        <v>6556343</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5175,22 +4535,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka yngra levande frihuggna almar. Inslag av gammal ek enstaka yngre ask och lönn.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5199,76 +4554,69 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>73746191</v>
+        <v>61381611</v>
       </c>
       <c r="B40" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>223246</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>636513.880450511</v>
+        <v>636482</v>
       </c>
       <c r="R40" t="n">
-        <v>6556287.780260329</v>
+        <v>6556347</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5292,22 +4640,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Enstaka friska almar och askar ca 60-70 år gamla.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5316,73 +4659,66 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>73746035</v>
+        <v>73746014</v>
       </c>
       <c r="B41" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>636516.7799732704</v>
+        <v>636545</v>
       </c>
       <c r="R41" t="n">
-        <v>6556249.863879045</v>
+        <v>6556187</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5412,19 +4748,9 @@
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5445,61 +4771,55 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>73746192</v>
+        <v>73746018</v>
       </c>
       <c r="B42" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636513.880450511</v>
+        <v>636539</v>
       </c>
       <c r="R42" t="n">
-        <v>6556287.780260329</v>
+        <v>6556200</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5529,19 +4849,9 @@
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5562,44 +4872,39 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>73746032</v>
+        <v>61381309</v>
       </c>
       <c r="B43" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92244</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>721</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Korallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Grifola frondosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Gray</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5607,17 +4912,17 @@
       <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636516.7799732704</v>
+        <v>636734</v>
       </c>
       <c r="R43" t="n">
-        <v>6556249.863879045</v>
+        <v>6556250</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5641,22 +4946,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ca 2x2dm vid roten på gammal ek.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5672,69 +4972,71 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>73746059</v>
+        <v>54527501</v>
       </c>
       <c r="B44" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>1079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>636713.0170853264</v>
+        <v>636696</v>
       </c>
       <c r="R44" t="n">
-        <v>6556174.163268562</v>
+        <v>6556179</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5758,22 +5060,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ca 5 dm2 vid basen av äldre lönn och ca 4 dm2 2m över marken, norra sidan. Strax norr om bilväg. Lönnen och en stor del av ädellövträden nyligen frihuggna. Möjligen mer mossa högre upp på lönnen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5782,34 +5079,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>73746176</v>
+        <v>61379079</v>
       </c>
       <c r="B45" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5840,17 +5131,17 @@
       <c r="L45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>V yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>636599.0633518201</v>
+        <v>636713</v>
       </c>
       <c r="R45" t="n">
-        <v>6556251.778668512</v>
+        <v>6556180</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5874,22 +5165,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Samma fynd som 2015. Vid roten av gammal lönn ca 2x3dm och ca 1x5dm ca 2m över marken på norra sidan av trädet. Även lunglav på samma träd.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5898,34 +5184,28 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>73746160</v>
+        <v>61381396</v>
       </c>
       <c r="B46" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5956,17 +5236,17 @@
       <c r="L46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>636596.7869340511</v>
+        <v>636596</v>
       </c>
       <c r="R46" t="n">
-        <v>6556257.862686821</v>
+        <v>6556255</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5990,22 +5270,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Nytt fynd vid basen av död ask mellan två block, 25cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6014,74 +5289,69 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>73746028</v>
+        <v>61381435</v>
       </c>
       <c r="B47" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>1079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>636516.7799732704</v>
+        <v>636600</v>
       </c>
       <c r="R47" t="n">
-        <v>6556249.863879045</v>
+        <v>6556246</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6105,22 +5375,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Nytt fynd på västra sidan av stammen på äldre lönn, från marken och upp till ca 1m över marken. Brösthöjdsdiameter 25cm.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6129,76 +5394,69 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>73746170</v>
+        <v>61381465</v>
       </c>
       <c r="B48" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221235</v>
+        <v>1079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>636596.7869340511</v>
+        <v>636591</v>
       </c>
       <c r="R48" t="n">
-        <v>6556257.862686821</v>
+        <v>6556238</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6222,22 +5480,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Nytt fynd på östra sidan av äldre lönn. Ca 15x20cm, 1m över marken. Brösthöjdsdiameter 30cm.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6246,76 +5499,69 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>73746056</v>
+        <v>61381531</v>
       </c>
       <c r="B49" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221235</v>
+        <v>1079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>636713.0170853264</v>
+        <v>636608</v>
       </c>
       <c r="R49" t="n">
-        <v>6556174.163268562</v>
+        <v>6556230</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6339,22 +5585,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Nytt fynd runt om stammen på en äldre lönn, från marken upp till 90cm över mark. Brösthöjdsdiameter 28cm.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6363,76 +5604,69 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>73746042</v>
+        <v>61381554</v>
       </c>
       <c r="B50" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221235</v>
+        <v>1079</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>Sarvsjön, NO om, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>636516.7799732704</v>
+        <v>636622</v>
       </c>
       <c r="R50" t="n">
-        <v>6556249.863879045</v>
+        <v>6556211</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6456,22 +5690,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Nytt fynd på södra sidan av äldre lönn, ca 10x15cm, 1,7m över marken.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6480,71 +5709,66 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>73746052</v>
+        <v>73746055</v>
       </c>
       <c r="B51" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1079</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>636713.0170853264</v>
+        <v>636713</v>
       </c>
       <c r="R51" t="n">
-        <v>6556174.163268562</v>
+        <v>6556174</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6574,19 +5798,9 @@
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6614,15 +5828,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>73746055</v>
+        <v>73746150</v>
       </c>
       <c r="B52" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6657,10 +5866,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>636713.0170853264</v>
+        <v>636597</v>
       </c>
       <c r="R52" t="n">
-        <v>6556174.163268562</v>
+        <v>6556287</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6690,19 +5899,9 @@
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6730,52 +5929,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>73746038</v>
+        <v>73746160</v>
       </c>
       <c r="B53" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6463</v>
+        <v>1079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>636516.7799732704</v>
+        <v>636597</v>
       </c>
       <c r="R53" t="n">
-        <v>6556249.863879045</v>
+        <v>6556258</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6805,19 +6000,9 @@
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6845,15 +6030,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>73746183</v>
+        <v>73746176</v>
       </c>
       <c r="B54" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6884,14 +6064,14 @@
       <c r="L54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>V Yngsviken, Srm</t>
+          <t>V yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>636585.9733916385</v>
+        <v>636599</v>
       </c>
       <c r="R54" t="n">
-        <v>6556229.217546627</v>
+        <v>6556252</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6921,19 +6101,9 @@
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6961,52 +6131,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>73746040</v>
+        <v>73746181</v>
       </c>
       <c r="B55" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6457</v>
+        <v>1079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>V Yngsviken, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>636516.7799732704</v>
+        <v>636610</v>
       </c>
       <c r="R55" t="n">
-        <v>6556249.863879045</v>
+        <v>6556240</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7036,19 +6202,9 @@
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7073,6 +6229,3737 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>73746183</v>
+      </c>
+      <c r="B56" t="n">
+        <v>96446</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1079</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Aspfjädermossa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neckera pennata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>636586</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6556229</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>73746134</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92510</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blekticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Haploporus tuberculosus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>636766</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6556283</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>61378955</v>
+      </c>
+      <c r="B58" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>636705</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6556196</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På gammal ek.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>61379082</v>
+      </c>
+      <c r="B59" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>636800</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6556197</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På gammal ek strax norr om väg.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>73746124</v>
+      </c>
+      <c r="B60" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>636774</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6556298</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>73746142</v>
+      </c>
+      <c r="B61" t="n">
+        <v>97394</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>636715</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6556287</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>54527890</v>
+      </c>
+      <c r="B62" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>636808</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6556166</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Block.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61381184</v>
+      </c>
+      <c r="B63" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>636811</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6556169</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På liten nordvänd lodyta.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>61381534</v>
+      </c>
+      <c r="B64" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>636608</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6556230</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På äldre lönn.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>61381558</v>
+      </c>
+      <c r="B65" t="n">
+        <v>96231</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>636622</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6556211</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På äldre lönn.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>61379091</v>
+      </c>
+      <c r="B66" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>636793</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6556159</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På gammal ek. Ringbarka konkurrerande gran.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>73746128</v>
+      </c>
+      <c r="B67" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>636774</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6556298</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>73746167</v>
+      </c>
+      <c r="B68" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>636597</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6556258</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>54527447</v>
+      </c>
+      <c r="B69" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>636695</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6556182</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Gammal ek., nyligen frihuggen.</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>54527514</v>
+      </c>
+      <c r="B70" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>636696</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6556179</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På samma lönn som aspfjädermossan.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>54527561</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>636708</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6556172</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre lönn</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>54527648</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>636750</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6556176</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Högt upp på äldre lönn. Strax norr om bilväg.</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>54527875</v>
+      </c>
+      <c r="B73" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>636808</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6556166</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Gammal lind.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>61379080</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>636713</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6556180</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På gammal lönn.</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>61381163</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>636813</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6556172</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På östra sidan av stammen på grov lind ca 5m över marken och på en gren i samma höjd. Strax söder om vägen. Troligen samma fynd som år 2015.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>73746052</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>636713</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6556174</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>54548048</v>
+      </c>
+      <c r="B77" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>636651</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6556240</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Två levande medelålders askar som nyligen frihuggits från konkurrerande barrträd.</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>61381315</v>
+      </c>
+      <c r="B78" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>636695</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6556256</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ca 70-årig ask med delvis torra grenar.</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>61381322</v>
+      </c>
+      <c r="B79" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>636662</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6556260</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Frisk ask ca 70 år gammal.</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>61378962</v>
+      </c>
+      <c r="B80" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>636711</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6556190</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Spridda fynd i området.</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>61379093</v>
+      </c>
+      <c r="B81" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>636793</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6556159</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Spridda fynd.</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>73746056</v>
+      </c>
+      <c r="B82" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>636713</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6556174</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>73746170</v>
+      </c>
+      <c r="B83" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>636597</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6556258</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>61381728</v>
+      </c>
+      <c r="B84" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>636606</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6556200</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Enstaka fyndplatser på kalkhaltig mark.</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>73770578</v>
+      </c>
+      <c r="B85" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>636610</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6556205</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2018-10-29</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2018-10-29</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>54547951</v>
+      </c>
+      <c r="B86" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>636713</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6556265</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2015-07-22</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Källpåverkad strandzon med en liten ringsatt källa.</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>61378945</v>
+      </c>
+      <c r="B87" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>636682</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6556156</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Enstaka fynd.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>61378960</v>
+      </c>
+      <c r="B88" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>636705</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6556196</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Allmänt förekommande.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>61379095</v>
+      </c>
+      <c r="B89" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Sarvsjön, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>636793</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6556159</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2016-09-09</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Allmänt förekommande.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>73746059</v>
+      </c>
+      <c r="B90" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>V Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>636713</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6556174</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2018-10-27</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen, Beatrice Svensson Lindius</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>132494471</v>
+      </c>
+      <c r="B91" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>NV Yngsviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>636688</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6556157</v>
+      </c>
+      <c r="S91" t="n">
+        <v>20</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Vit variant.</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44309-2025 artfynd.xlsx
+++ b/artfynd/A 44309-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381657</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746018</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746220</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738380</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738381</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738383</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1479,6 +1519,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746197</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1583,6 +1628,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548193</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381720</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738385</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746234</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381309</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2114,6 +2184,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527501</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379079</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2324,6 +2404,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381396</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2429,6 +2514,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381435</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2534,6 +2624,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381465</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2639,6 +2734,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381531</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2744,6 +2844,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381554</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2845,6 +2950,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746055</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2946,6 +3056,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746150</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3047,6 +3162,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746160</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3148,6 +3268,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746176</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3249,6 +3374,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746181</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3350,6 +3480,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746183</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3450,6 +3585,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746134</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3554,6 +3694,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61378955</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3658,6 +3803,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379082</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3758,6 +3908,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738378</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3858,6 +4013,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746124</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3959,6 +4119,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746142</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4067,6 +4232,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548230</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4172,6 +4342,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527890</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4277,6 +4452,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381184</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4382,6 +4562,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381534</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4487,6 +4672,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381558</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4592,6 +4782,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381723</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4696,6 +4891,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379091</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4796,6 +4996,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73738379</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4896,6 +5101,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746128</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4996,6 +5206,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746167</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5096,6 +5311,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746196</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5196,6 +5416,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746214</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5300,6 +5525,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527447</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5400,6 +5630,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746237</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5500,6 +5735,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746040</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5604,6 +5844,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527514</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5708,6 +5953,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527561</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5812,6 +6062,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527648</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5916,6 +6171,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54527875</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6020,6 +6280,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548306</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6124,6 +6389,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379080</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6228,6 +6498,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381163</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6328,6 +6603,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746028</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6428,6 +6708,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746052</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6528,6 +6813,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746038</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6632,6 +6922,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548293</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6732,6 +7027,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746032</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6843,6 +7143,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548265</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6948,6 +7253,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548048</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7053,6 +7363,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548147</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7158,6 +7473,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381315</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7263,6 +7583,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381322</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7368,6 +7693,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381618</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7473,6 +7803,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61378962</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7578,6 +7913,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379093</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7683,6 +8023,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381592</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7785,6 +8130,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746042</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7887,6 +8237,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746056</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7989,6 +8344,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746170</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8091,6 +8451,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746192</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8196,6 +8561,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548179</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8296,6 +8666,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381579</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8401,6 +8776,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381728</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8503,6 +8883,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746190</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8605,6 +8990,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73770578</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8706,6 +9096,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548215</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8811,6 +9206,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54547951</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8916,6 +9316,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61378945</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9021,6 +9426,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61378960</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9126,6 +9536,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61379095</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9228,6 +9643,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746035</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9330,6 +9750,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746059</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9432,6 +9857,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746191</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9534,6 +9964,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73746245</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9645,6 +10080,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132494471</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9750,6 +10190,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548104</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9855,6 +10300,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54548136</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9960,8 +10410,105 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61381611</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>